--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460698</v>
+        <v>122460685</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566356</v>
+        <v>566408</v>
       </c>
       <c r="R2" t="n">
-        <v>6417479</v>
+        <v>6417491</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1023,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460640</v>
+        <v>122460698</v>
       </c>
       <c r="B5" t="n">
-        <v>91416</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,26 +1056,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566415</v>
+        <v>566356</v>
       </c>
       <c r="R5" t="n">
-        <v>6417525</v>
+        <v>6417479</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,13 +1108,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460685</v>
+        <v>122460640</v>
       </c>
       <c r="B7" t="n">
-        <v>57749</v>
+        <v>91416</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1286,27 +1286,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R7" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,6 +1343,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460600</v>
+        <v>122460683</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,29 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566419</v>
+        <v>566408</v>
       </c>
       <c r="R3" t="n">
-        <v>6417518</v>
+        <v>6417491</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460683</v>
+        <v>122460600</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,33 +919,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566408</v>
+        <v>566419</v>
       </c>
       <c r="R4" t="n">
-        <v>6417491</v>
+        <v>6417518</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,6 +987,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460698</v>
+        <v>122460640</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>91421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1056,27 +1056,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566356</v>
+        <v>566415</v>
       </c>
       <c r="R5" t="n">
-        <v>6417479</v>
+        <v>6417525</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,17 +1107,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1137,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460623</v>
+        <v>122460698</v>
       </c>
       <c r="B6" t="n">
-        <v>105303</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,35 +1144,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566400</v>
+        <v>566356</v>
       </c>
       <c r="R6" t="n">
-        <v>6417441</v>
+        <v>6417479</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,13 +1222,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1248,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460640</v>
+        <v>122460623</v>
       </c>
       <c r="B7" t="n">
-        <v>91416</v>
+        <v>105308</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,45 +1267,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566415</v>
+        <v>566400</v>
       </c>
       <c r="R7" t="n">
-        <v>6417525</v>
+        <v>6417441</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460640</v>
+        <v>122460623</v>
       </c>
       <c r="B5" t="n">
-        <v>91421</v>
+        <v>105308</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,45 +1034,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566415</v>
+        <v>566400</v>
       </c>
       <c r="R5" t="n">
-        <v>6417525</v>
+        <v>6417441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1251,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460623</v>
+        <v>122460640</v>
       </c>
       <c r="B7" t="n">
-        <v>105308</v>
+        <v>91421</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,42 +1264,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566400</v>
+        <v>566415</v>
       </c>
       <c r="R7" t="n">
-        <v>6417441</v>
+        <v>6417525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460685</v>
+        <v>122460698</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566408</v>
+        <v>566356</v>
       </c>
       <c r="R2" t="n">
-        <v>6417491</v>
+        <v>6417479</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460683</v>
+        <v>122460623</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>105317</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566408</v>
+        <v>566400</v>
       </c>
       <c r="R3" t="n">
-        <v>6417491</v>
+        <v>6417441</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460600</v>
+        <v>122460640</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>91426</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +907,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1339</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566419</v>
+        <v>566415</v>
       </c>
       <c r="R4" t="n">
-        <v>6417518</v>
+        <v>6417525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,17 +979,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460623</v>
+        <v>122460683</v>
       </c>
       <c r="B5" t="n">
-        <v>105308</v>
+        <v>57532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1016,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566400</v>
+        <v>566408</v>
       </c>
       <c r="R5" t="n">
-        <v>6417441</v>
+        <v>6417491</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1095,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460698</v>
+        <v>122460685</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,20 +1125,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1171,7 +1150,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1181,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566356</v>
+        <v>566408</v>
       </c>
       <c r="R6" t="n">
-        <v>6417479</v>
+        <v>6417491</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460640</v>
+        <v>122460600</v>
       </c>
       <c r="B7" t="n">
-        <v>91421</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,49 +1234,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566415</v>
+        <v>566419</v>
       </c>
       <c r="R7" t="n">
-        <v>6417525</v>
+        <v>6417518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,13 +1303,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460698</v>
+        <v>122460623</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>105330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566356</v>
+        <v>566400</v>
       </c>
       <c r="R2" t="n">
-        <v>6417479</v>
+        <v>6417441</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,17 +761,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460623</v>
+        <v>122460683</v>
       </c>
       <c r="B3" t="n">
-        <v>105317</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566400</v>
+        <v>566408</v>
       </c>
       <c r="R3" t="n">
-        <v>6417441</v>
+        <v>6417491</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460640</v>
+        <v>122460600</v>
       </c>
       <c r="B4" t="n">
-        <v>91426</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,44 +912,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566415</v>
+        <v>566419</v>
       </c>
       <c r="R4" t="n">
-        <v>6417525</v>
+        <v>6417518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,13 +986,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460683</v>
+        <v>122460640</v>
       </c>
       <c r="B5" t="n">
-        <v>57532</v>
+        <v>91439</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,48 +1027,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1339</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R5" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,6 +1110,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,7 +1132,7 @@
         <v>122460685</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,6 +1146,11 @@
       </c>
       <c r="E6" t="n">
         <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1222,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460600</v>
+        <v>122460698</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,6 +1261,11 @@
       <c r="E7" t="n">
         <v>100049</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1250,12 +1276,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1265,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566419</v>
+        <v>566356</v>
       </c>
       <c r="R7" t="n">
-        <v>6417518</v>
+        <v>6417479</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460623</v>
+        <v>122460640</v>
       </c>
       <c r="B2" t="n">
-        <v>105330</v>
+        <v>91452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566400</v>
+        <v>566415</v>
       </c>
       <c r="R2" t="n">
-        <v>6417441</v>
+        <v>6417525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460683</v>
+        <v>122460698</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,33 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -838,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566408</v>
+        <v>566356</v>
       </c>
       <c r="R3" t="n">
-        <v>6417491</v>
+        <v>6417479</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460600</v>
+        <v>122460623</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +920,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566419</v>
+        <v>566400</v>
       </c>
       <c r="R4" t="n">
-        <v>6417518</v>
+        <v>6417441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,17 +994,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460640</v>
+        <v>122460600</v>
       </c>
       <c r="B5" t="n">
-        <v>91439</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,49 +1031,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566415</v>
+        <v>566419</v>
       </c>
       <c r="R5" t="n">
-        <v>6417525</v>
+        <v>6417518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,13 +1105,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460685</v>
+        <v>122460683</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,30 +1146,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460698</v>
+        <v>122460685</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,20 +1260,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1285,7 +1290,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1295,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566356</v>
+        <v>566408</v>
       </c>
       <c r="R7" t="n">
-        <v>6417479</v>
+        <v>6417491</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,11 +1336,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460640</v>
+        <v>122460623</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>105343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566415</v>
+        <v>566400</v>
       </c>
       <c r="R2" t="n">
-        <v>6417525</v>
+        <v>6417441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460698</v>
+        <v>122460683</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,33 +802,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566356</v>
+        <v>566408</v>
       </c>
       <c r="R3" t="n">
-        <v>6417479</v>
+        <v>6417491</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460623</v>
+        <v>122460698</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566400</v>
+        <v>566356</v>
       </c>
       <c r="R4" t="n">
-        <v>6417441</v>
+        <v>6417479</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,13 +990,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460683</v>
+        <v>122460685</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,30 +1146,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460685</v>
+        <v>122460640</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>91452</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1286,27 +1286,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R7" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,6 +1343,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460623</v>
+        <v>122460683</v>
       </c>
       <c r="B2" t="n">
-        <v>105343</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566400</v>
+        <v>566408</v>
       </c>
       <c r="R2" t="n">
-        <v>6417441</v>
+        <v>6417491</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460683</v>
+        <v>122460623</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>105346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566408</v>
+        <v>566400</v>
       </c>
       <c r="R3" t="n">
-        <v>6417491</v>
+        <v>6417441</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460600</v>
+        <v>122460685</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,20 +1031,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,12 +1052,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1067,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566419</v>
+        <v>566408</v>
       </c>
       <c r="R5" t="n">
-        <v>6417518</v>
+        <v>6417491</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,11 +1107,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460685</v>
+        <v>122460600</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,20 +1145,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,16 +1166,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1186,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566408</v>
+        <v>566419</v>
       </c>
       <c r="R6" t="n">
-        <v>6417491</v>
+        <v>6417518</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,6 +1217,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
         <v>122460640</v>
       </c>
       <c r="B7" t="n">
-        <v>91452</v>
+        <v>91453</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460683</v>
+        <v>122460685</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460623</v>
+        <v>122460640</v>
       </c>
       <c r="B3" t="n">
-        <v>105346</v>
+        <v>91453</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,42 +805,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566400</v>
+        <v>566415</v>
       </c>
       <c r="R3" t="n">
-        <v>6417441</v>
+        <v>6417525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1019,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460685</v>
+        <v>122460623</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>105346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,35 +1038,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566408</v>
+        <v>566400</v>
       </c>
       <c r="R5" t="n">
-        <v>6417491</v>
+        <v>6417441</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,6 +1114,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460600</v>
+        <v>122460683</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,29 +1149,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566419</v>
+        <v>566408</v>
       </c>
       <c r="R6" t="n">
-        <v>6417518</v>
+        <v>6417491</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,11 +1221,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460640</v>
+        <v>122460600</v>
       </c>
       <c r="B7" t="n">
-        <v>91453</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,49 +1259,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566415</v>
+        <v>566419</v>
       </c>
       <c r="R7" t="n">
-        <v>6417525</v>
+        <v>6417518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,13 +1333,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460685</v>
+        <v>122460683</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460640</v>
+        <v>122460685</v>
       </c>
       <c r="B3" t="n">
-        <v>91453</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,26 +827,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566415</v>
+        <v>566408</v>
       </c>
       <c r="R3" t="n">
-        <v>6417525</v>
+        <v>6417491</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460698</v>
+        <v>122460640</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>91454</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,27 +941,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566356</v>
+        <v>566415</v>
       </c>
       <c r="R4" t="n">
-        <v>6417479</v>
+        <v>6417525</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,17 +992,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460623</v>
+        <v>122460600</v>
       </c>
       <c r="B5" t="n">
-        <v>105346</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,35 +1029,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566400</v>
+        <v>566419</v>
       </c>
       <c r="R5" t="n">
-        <v>6417441</v>
+        <v>6417518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,13 +1103,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460683</v>
+        <v>122460698</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,33 +1148,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1185,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566408</v>
+        <v>566356</v>
       </c>
       <c r="R6" t="n">
-        <v>6417491</v>
+        <v>6417479</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,6 +1220,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460600</v>
+        <v>122460623</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>105347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,35 +1263,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566419</v>
+        <v>566400</v>
       </c>
       <c r="R7" t="n">
-        <v>6417518</v>
+        <v>6417441</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,17 +1337,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460683</v>
+        <v>122460685</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460685</v>
+        <v>122460600</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,16 +822,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566408</v>
+        <v>566419</v>
       </c>
       <c r="R3" t="n">
-        <v>6417491</v>
+        <v>6417518</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460640</v>
+        <v>122460683</v>
       </c>
       <c r="B4" t="n">
-        <v>91454</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,52 +916,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566415</v>
+        <v>566408</v>
       </c>
       <c r="R4" t="n">
-        <v>6417525</v>
+        <v>6417491</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1000,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460600</v>
+        <v>122460640</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,46 +1030,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566419</v>
+        <v>566415</v>
       </c>
       <c r="R5" t="n">
-        <v>6417518</v>
+        <v>6417525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,17 +1107,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>122460623</v>
       </c>
       <c r="B7" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460685</v>
+        <v>122460600</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566408</v>
+        <v>566419</v>
       </c>
       <c r="R2" t="n">
-        <v>6417491</v>
+        <v>6417518</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460600</v>
+        <v>122460698</v>
       </c>
       <c r="B3" t="n">
         <v>57400</v>
@@ -822,12 +823,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566419</v>
+        <v>566356</v>
       </c>
       <c r="R3" t="n">
-        <v>6417518</v>
+        <v>6417479</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460683</v>
+        <v>122460685</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,30 +921,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1132,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460698</v>
+        <v>122460623</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>105350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566356</v>
+        <v>566400</v>
       </c>
       <c r="R6" t="n">
-        <v>6417479</v>
+        <v>6417441</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,17 +1223,13 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1251,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460623</v>
+        <v>122460683</v>
       </c>
       <c r="B7" t="n">
-        <v>105350</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,35 +1260,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566400</v>
+        <v>566408</v>
       </c>
       <c r="R7" t="n">
-        <v>6417441</v>
+        <v>6417491</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,7 +1344,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460685</v>
+        <v>122460640</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,27 +947,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R4" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460640</v>
+        <v>122460685</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,26 +1061,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566415</v>
+        <v>566408</v>
       </c>
       <c r="R5" t="n">
-        <v>6417525</v>
+        <v>6417491</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1119,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460640</v>
+        <v>122460685</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>57754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,26 +947,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566415</v>
+        <v>566408</v>
       </c>
       <c r="R4" t="n">
-        <v>6417525</v>
+        <v>6417491</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460685</v>
+        <v>122460640</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,27 +1061,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R5" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,6 +1118,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460600</v>
+        <v>122460685</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566419</v>
+        <v>566408</v>
       </c>
       <c r="R2" t="n">
-        <v>6417518</v>
+        <v>6417491</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460698</v>
+        <v>122460600</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,16 +822,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566356</v>
+        <v>566419</v>
       </c>
       <c r="R3" t="n">
-        <v>6417479</v>
+        <v>6417518</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tyst bland barkborregranarna.</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460685</v>
+        <v>122460683</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,30 +916,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1023,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460640</v>
+        <v>122460623</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>105453</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,45 +1034,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566415</v>
+        <v>566400</v>
       </c>
       <c r="R5" t="n">
-        <v>6417525</v>
+        <v>6417441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460623</v>
+        <v>122460640</v>
       </c>
       <c r="B6" t="n">
-        <v>105350</v>
+        <v>91560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,42 +1145,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566400</v>
+        <v>566415</v>
       </c>
       <c r="R6" t="n">
-        <v>6417441</v>
+        <v>6417525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460683</v>
+        <v>122460698</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,33 +1259,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1300,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566408</v>
+        <v>566356</v>
       </c>
       <c r="R7" t="n">
-        <v>6417491</v>
+        <v>6417479</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,6 +1331,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460685</v>
+        <v>122460640</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>91564</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +713,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R2" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460600</v>
+        <v>122460685</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,12 +822,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566419</v>
+        <v>566408</v>
       </c>
       <c r="R3" t="n">
-        <v>6417518</v>
+        <v>6417491</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460683</v>
+        <v>122460623</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>105461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566408</v>
+        <v>566400</v>
       </c>
       <c r="R4" t="n">
-        <v>6417491</v>
+        <v>6417441</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460623</v>
+        <v>122460600</v>
       </c>
       <c r="B5" t="n">
-        <v>105453</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566400</v>
+        <v>566419</v>
       </c>
       <c r="R5" t="n">
-        <v>6417441</v>
+        <v>6417518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,13 +1100,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460640</v>
+        <v>122460683</v>
       </c>
       <c r="B6" t="n">
-        <v>91560</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,52 +1141,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566415</v>
+        <v>566408</v>
       </c>
       <c r="R6" t="n">
-        <v>6417525</v>
+        <v>6417491</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 955-2025 artfynd.xlsx
+++ b/artfynd/A 955-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460640</v>
+        <v>122460623</v>
       </c>
       <c r="B2" t="n">
-        <v>91564</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
+          <t>A 955, Rösslestugan, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566415</v>
+        <v>566400</v>
       </c>
       <c r="R2" t="n">
-        <v>6417525</v>
+        <v>6417441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460685</v>
+        <v>122460640</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>91564</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,27 +824,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 955, Rösslestugan, Odensvi, Sm</t>
+          <t>A 955, Rösslestugan, Oodensvi, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566408</v>
+        <v>566415</v>
       </c>
       <c r="R3" t="n">
-        <v>6417491</v>
+        <v>6417525</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460623</v>
+        <v>122460698</v>
       </c>
       <c r="B4" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566400</v>
+        <v>566356</v>
       </c>
       <c r="R4" t="n">
-        <v>6417441</v>
+        <v>6417479</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,13 +990,17 @@
           <t>2025-02-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tyst bland barkborregranarna.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460683</v>
+        <v>122460685</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,30 +1146,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460698</v>
+        <v>122460683</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,33 +1264,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1295,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566356</v>
+        <v>566408</v>
       </c>
       <c r="R7" t="n">
-        <v>6417479</v>
+        <v>6417491</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,11 +1336,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tyst bland barkborregranarna.</t>
         </is>
       </c>
       <c r="AD7" t="b">
